--- a/review/etnografiya/may-december/calendar-year.xlsx
+++ b/review/etnografiya/may-december/calendar-year.xlsx
@@ -117,7 +117,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как на домашней ёлке встретились дореволюционный ангел и советская ракета?</t>
+          <t xml:space="preserve">На одной домашней ёлке соседствуют ангел и ракета. Маленькие игрушки сохраняют следы больших перемен в жизни русской семьи.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -144,7 +144,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">До скотного двора можно дойти, не выходя под снег. Как жила семья в таком доме?</t>
+          <t xml:space="preserve">Семья идёт к скотному двору, не выходя под снег. Северный дом собирает жильё и хозяйство под одной крышей — мороз меняет сам план жизни.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -171,7 +171,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">У этого цветка горели три бутона. Зачем под него ставили корыто с водой?</t>
+          <t xml:space="preserve">У железного цветка горят три бутона-лучины. Корыто с водой внизу выдаёт цену домашнего света: за каждым огоньком приходилось следить.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -198,7 +198,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горшок раскалён, а ручек нет. Как поставить ужин на стол?</t>
+          <t xml:space="preserve">Горшок раскалён, а ручек нет. Железная рогатина ухвата позволяет достать ужин из глубины печи — работа держится на точном движении рук.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ни подошвы, ни шва — а получился сапог. Что сделали с обычной шерстью?</t>
+          <t xml:space="preserve">Ни подошвы, ни шва — а получился сапог. Мастер уплотняет шерсть в валенок: мягкие волокна становятся защитой от русского зимнего холода.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -252,7 +252,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">До Рождества — одна ночь. Почему праздничный стол ещё остаётся постным?</t>
+          <t xml:space="preserve">До Рождества одна ночь, а стол ещё постный. Сочельник отделяет ожидание от праздника — семейная трапеза хранит этот переход.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -279,7 +279,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Звезда была не только на ёлке: с ней стучались в соседские двери. Зачем?</t>
+          <t xml:space="preserve">Рождественскую звезду несут от дома к дому. Праздник выходит за семейный стол: соседскую дверь открывают песне и доброму пожеланию.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -306,7 +306,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">После Рождества чествовали женщину, которая помогла тебе появиться на свет. Чем её благодарили?</t>
+          <t xml:space="preserve">После Рождества благодарят женщину, помогавшую детям появиться на свет. За праздничным обычаем стоит труд повивальной бабки.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -333,7 +333,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">За пожелание доброго года открывали дверь и давали угощение. Что связывало хозяев и певцов?</t>
+          <t xml:space="preserve">Певцы приносят пожелание доброго года, хозяева отвечают угощением. Святки превращают соседскую дверь в место взаимного дара.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -360,7 +360,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рождественское пожелание в Архангельске можно было подарить в виде пряника?</t>
+          <t xml:space="preserve">Рождественское пожелание можно испечь и подарить. Архангельская козуля соединяет пряничное ремесло, праздничный образ и тепло рук.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -387,7 +387,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бархатное сиденье, бахрома, меховой полог. Зачем саням столько наряда?</t>
+          <t xml:space="preserve">Бархат, бахрома и мех едут по снегу. Нарядные сани превращают зимнюю дорогу в выход на люди — мастерство видно ещё до остановки.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -414,7 +414,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кумачовая рубаха, жилет и картуз: что выдавало деревенского модника?</t>
+          <t xml:space="preserve">Кумачовая рубаха, жилет и картуз собираются в праздничный образ. Деревенский наряд хранит собственный язык щегольства и достоинства.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кольцо вытаскивают наугад, а смысл даёт песня. О чём девушки хотели узнать?</t>
+          <t xml:space="preserve">Кольцо достают наугад, а толкование задаёт песня. Подблюдное гадание сохраняет девичьи ожидания будущего, а не знание о грядущем.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">На улице снег, а зерно разбрасывают прямо в доме. Какого урожая здесь ждут?</t>
+          <t xml:space="preserve">За окном снег, а в доме разбрасывают зерно. Зимнее пожелание урожая переносит заботу о будущем поле прямо к семейному порогу.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тулуп вывернут, лицо скрыто. Почему знакомый человек должен был стать неузнаваемым?</t>
+          <t xml:space="preserve">Тулуп вывернут, лицо скрыто — соседа трудно узнать. Ряженье позволяет знакомому человеку ненадолго войти в праздничную чужую роль.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Драгоценный венец — у деревенской девушки. Как его делали и когда надевали?</t>
+          <t xml:space="preserve">Деревенская девушка надевает нарядный венец. В маленьких деталях убора соединяются мастерство рук и торжественность выхода на люди.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">За бревенчатыми стенами — парадная зала. Как деревенская семья показывала связь с Петербургом?</t>
+          <t xml:space="preserve">За бревенчатыми стенами открывается парадная зала. Северный дом хранит городской след: связь с Петербургом читается в его интерьере.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крест, ковш и ведро встретились на одной выставке. Что связывает их с зимним праздником?</t>
+          <t xml:space="preserve">Крест, ковш и ведро оказываются рядом. Крещенский праздник связывает церковный обряд с простыми вещами, которыми набирали и хранили воду.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему зимняя прорубь получила имя далёкой реки?</t>
+          <t xml:space="preserve">Зимнюю прорубь называют Иорданью. Имя далёкой реки входит в русский зимний пейзаж через память о Крещении и местный праздничный обряд.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семья пьёт чай, рядом колокольня и двуглавый орёл. Зачем всё это вырезали на прялке?</t>
+          <t xml:space="preserve">На прялке вырезаны чаепитие, колокольня и двуглавый орёл. Рабочая вещь становится маленькой картиной мира, оставленной мастером.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прялка стоит неподвижно. Что же на самом деле превращает волокно в нить?</t>
+          <t xml:space="preserve">Прялка удерживает волокно, а веретено скручивает нить. За привычным названием скрыта работа двух разных предметов и умелых пальцев.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эта ребристая доска не стирает. Как она расправляет жёсткое бельё?</t>
+          <t xml:space="preserve">Ребристая доска расправляет бельё без горячей подошвы. Рубель работает вместе с валиком: тяжёлый домашний труд превращён в точный приём.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поднял дощечку, опустил — и нити поменялись местами. Как из этого получается пояс?</t>
+          <t xml:space="preserve">Дощечка поднимается — нити меняются местами. В узком поясе остаётся порядок движений ткачихи: рисунок рождается из переплетения.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перед нами русские женские наряды — а привычного сарафана нет. Что рассказывает клетчатая понёва?</t>
+          <t xml:space="preserve">Перед нами русский женский наряд без сарафана. Клетчатая понёва открывает другой крой и местную традицию, которую нельзя свести к одной картинке.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Университетский праздник вышел на московские улицы. Что делало чужих людей «старыми студентами»?</t>
+          <t xml:space="preserve">Университетский праздник выходит на московские улицы. Встреча «старых студентов» связывает людей, чьи годы учёбы давно остались позади.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вода окружает огонь, но не гасит его. Что спрятано внутри самовара?</t>
+          <t xml:space="preserve">Вода окружает огонь, но не гасит его. Внутри самовара проходит жаровая труба — семейное чаепитие начинается с продуманного устройства.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кору сняли летом, а зимой из неё делают домашнюю утварь. Как ленты держатся без ткани?</t>
+          <t xml:space="preserve">Берестяные ленты переплетаются без нитки и ткани. Снятая летом кора становится домашней утварью: гибкость материала работает на мастера.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Несколько зарубок — и в куске дерева уже виден конь. Как мастер замечает его раньше нас?</t>
+          <t xml:space="preserve">Несколько зарубок — и в дереве проступает конь. Мастер убирает лишнее так, что маленькая игрушка сохраняет узнаваемый характер животного.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дом можно перевезти только по брёвнышку. А как переселенцы увезли с собой общий голос?</t>
+          <t xml:space="preserve">Дом перевозят по брёвнышку, а песню уносят в памяти. Общий голос помогает переселенцам сохранять связь с оставленной родиной.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снаружи мороз, а на сундуке цветут яркие букеты. Как роспись меняла домашний мир?</t>
+          <t xml:space="preserve">Снаружи мороз, на сундуке цветут букеты. Роспись превращает место хранения вещей в яркий домашний мир, созданный человеческими руками.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">За месяц мы разобрали столько вещей. Сможешь теперь увидеть труд за обычной полоской ткани?</t>
+          <t xml:space="preserve">За полоской ткани скрываются прядение, ткачество и отделка. Обычная вещь становится видимой цепочкой труда — от волокна до семейного дома.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему одного визита могло быть недостаточно?</t>
+          <t xml:space="preserve">Сватовство не обязательно заканчивается первым визитом. Свадебная договорённость складывается по местному порядку, соединяя несколько действий и встреч.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что могли узнавать о будущей семье до свадьбы?</t>
+          <t xml:space="preserve">Перед браком знакомятся с другим хозяйством. Смотр дома показывает, что новая семейная связь касается повседневного устройства жизни.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как люди обозначали, что договорённость состоялась?</t>
+          <t xml:space="preserve">Рукобитье делает договорённость видимой. Жест становится частью местного свадебного порядка, по которому окружающие узнают о принятом решении.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у большого обряда так много помощников?</t>
+          <t xml:space="preserve">Дружка, сваха и подруги выполняют разные свадебные роли. Общий праздник держится на людях, которым поручены конкретные действия.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сообщить о событии без общего чата?</t>
+          <t xml:space="preserve">Приглашение разносит свадебную новость по селу. Будущая встреча начинается раньше застолья — с личного обращения и принятого способа звать гостей.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в общении подруг перед свадьбой?</t>
+          <t xml:space="preserve">Девичник собирает прежний круг перед переменой. Праздничная встреча сохраняет момент, когда отношения подруг получают новое продолжение.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему волосы становятся частью семейного обряда?</t>
+          <t xml:space="preserve">Невестина причёска меняется в ходе свадьбы. Волосы становятся видимым знаком перехода, который местная традиция оформляет определёнными действиями.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему на свадьбе можно услышать плач?</t>
+          <t xml:space="preserve">Свадебное причитание допускает печаль внутри праздника. Голос выражает переживание перемены, не отменяя радости общего события.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как услышать различие без музыкального образования?</t>
+          <t xml:space="preserve">Причитание и песня по-разному организуют речь. В свадебной записи слышно, как человеческое переживание получает разные музыкальные формы.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему вокруг небольшой украшенной вещи строится эпизод?</t>
+          <t xml:space="preserve">Свадебное деревце собирает вокруг себя действия участников. Небольшой предмет становится опорой местного обряда и последовательности встречи.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как обычная полоска ткани становится памятной?</t>
+          <t xml:space="preserve">Лента невесты связана с прежним девичеством. Передача или смена украшения превращает личную вещь в знак перемены семейного положения.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто участвует в приготовлении и разделе хлеба?</t>
+          <t xml:space="preserve">Каравай включён в общее свадебное действие. Праздничная еда получает смысл через приготовление, встречу и участие конкретных людей.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что поют не для сцены, а для события?</t>
+          <t xml:space="preserve">Каравайная песня сопровождает работу рук. Приготовление свадебного хлеба соединяет общий голос с последовательностью домашнего дела.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздник связан с разговорами о будущей семье?</t>
+          <t xml:space="preserve">Покров входит в народные свадебные ожидания осени. Праздничная дата хранит сезонную связь семейных надежд с завершением части хозяйственных работ.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему дорога между домами становится частью праздника?</t>
+          <t xml:space="preserve">Свадебный поезд делает переход видимым для деревни. Движение между домами связывает личное семейное событие с пространством всего поселения.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как трапеза выражает отношение к гостю?</t>
+          <t xml:space="preserve">Хлебом и солью встречают входящих в дом. Привычные продукты становятся частью принятия человека и открытого обращения хозяев к гостю.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что надевают после изменения причёски?</t>
+          <t xml:space="preserve">Свадебный убор меняет прежний вид невесты. Слои одежды оформляют переход, который окружающие считывают по местным правилам костюма.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в комнате не все места равноценны?</t>
+          <t xml:space="preserve">В красном углу собираются значимые домашние предметы. Порядок комнаты выделяет место, к которому обращаются в важных семейных обстоятельствах.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что может означать место человека на семейном пиру?</t>
+          <t xml:space="preserve">Рассадка делает отношения видимыми за столом. Место гостя связано с местным порядком встречи — близость к другому человеку не случайна.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как песня обращается к конкретному гостю?</t>
+          <t xml:space="preserve">Величальная песня называет достоинства человека. Праздничный голос обращает внимание собрания на того, кому адресованы слова.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему свадебная насмешка понятна участникам обряда?</t>
+          <t xml:space="preserve">Корильная песня включает шутку в свадебное общение. Её смысл зависит от ситуации и границ, которые признают участники конкретной традиции.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как обмен вещами укрепляет новые связи?</t>
+          <t xml:space="preserve">На свадебный дар отвечают отдариванием. Вещь проходит между людьми и поддерживает связь, которая не исчерпывается одной передачей подарка.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется название одного человека для разных родственников?</t>
+          <t xml:space="preserve">После свадьбы появляются новые названия родства. Свекровь, тёща и зять обозначают разные связи внутри расширившегося семейного круга.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие привычные действия становятся непривычными на новом месте?</t>
+          <t xml:space="preserve">Первое утро в новом доме продолжает свадебную перемену. За торжественным переходом начинается знакомство с повседневным порядком другой семьи.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему нельзя собрать русскую свадьбу из случайных обычаев?</t>
+          <t xml:space="preserve">В Большебыкове свадьба имеет свой порядок. Местная запись сохраняет конкретные роли и действия, которые нельзя автоматически приписать всем русским сёлам.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как семейный обряд живёт в переселенческой среде?</t>
+          <t xml:space="preserve">Русская свадьба Томского Приобья живёт вдали от прежней родины. Запись позволяет увидеть местное продолжение семейной традиции в новом окружении.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что даёт запись людей, а не только пересказ обряда?</t>
+          <t xml:space="preserve">Северная свадьба Кебы сохраняется в голосах села. Имена исполнителей и обстоятельства записи возвращают обряду конкретное человеческое место.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему название традиции охватывает несколько поселений?</t>
+          <t xml:space="preserve">Локня и Ловать задают географию свадебных записей. Речная карта помогает различать местные варианты вместо одной собирательной церемонии.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что остаётся, если обряд перестали исполнять целиком?</t>
+          <t xml:space="preserve">Запись из Сланцевского района удерживает семейный обряд во времени. Слышимый голос связывает исследование традиции с конкретным исполнителем.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что изменилось в одежде и способе хранить память?</t>
+          <t xml:space="preserve">Городское свадебное фото выбирает новые позы и декорации. Семейное событие получает другой визуальный язык, сохраняя желание оставить память о встрече.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли рассказать о близких, не зная их точных слов?</t>
+          <t xml:space="preserve">Семейная история складывается из снимков, подписей и свидетельств. Отсутствующий разговор остаётся неизвестным — память сильнее без выдуманной цитаты.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему лаковая коробочка начинается не с дерева?</t>
+          <t xml:space="preserve">Бумага становится прочной федоскинской шкатулкой. Под живописью скрыта работа с основой — привычный материал получает неожиданную долговечную форму.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как глубина появляется на плоской крышке?</t>
+          <t xml:space="preserve">Блеск под федоскинской живописью меняет вид изображения. Свет проходит через художественные слои и становится частью мастерского замысла.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как разместить несколько эпизодов в ладони?</t>
+          <t xml:space="preserve">На маленькой палехской крышке помещается большой сюжет. Масштаб миниатюры требует точности, чтобы фигуры и события оставались различимыми.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему похожие коробочки имеют разные авторские почерки?</t>
+          <t xml:space="preserve">Холуйская миниатюра сохраняет почерк местной школы. Общий вид ремесла не стирает различий в том, как мастера строят изображение.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как окружение помогает прочитать сюжет?</t>
+          <t xml:space="preserve">Мстёрский пейзаж окружает действие миниатюры. Маленькая поверхность вмещает пространство, в котором фигуры получают своё место и направление движения.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему маленькое украшение требует нескольких стадий?</t>
+          <t xml:space="preserve">Цвет ростовской финифти проходит через обжиг. Изображение возникает не одним движением кисти — огонь участвует в работе мастера.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как металл выглядит лёгким кружевом?</t>
+          <t xml:space="preserve">Металлическая нить складывается в ажурную скань. Твёрдый материал выглядит лёгким благодаря изгибам, соединениям и оставленным просветам.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как календарь возвращает семью к ушедшим поколениям?</t>
+          <t xml:space="preserve">Память о родных собирает людей вместе. Обычай Дмитриева дня возвращает внимание к семейной связи, которая продолжается за пределами одной жизни.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему тёмная линия делает узор заметнее?</t>
+          <t xml:space="preserve">Великоустюжская чернь создаёт тёмный рисунок на серебре. Различие поверхностей помогает прочитать тонкую работу на небольшой металлической вещи.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как имя святой входит в мир домашней работы?</t>
+          <t xml:space="preserve">Образ Параскевы Пятницы связан с женскими занятиями в народной традиции. Почитание получает местное выражение в отношении к труду и его ритму.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как металлическая нить держится на ткани?</t>
+          <t xml:space="preserve">Блестящая нить торжокского шитья удерживается на ткани стежками. Под нарядной поверхностью находится точный порядок закрепления материала.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как убрать часть нитей и сохранить ткань?</t>
+          <t xml:space="preserve">В крестецкой строчке часть нитей убирают ради узора. Просветы становятся рисунком, а оставшиеся соединения удерживают ткань целой.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что соединяет крупные элементы узора?</t>
+          <t xml:space="preserve">Мелкая сетка елецкого кружева связывает крупные мотивы. Воздушный рисунок держится на деталях, которые легко пропустить при первом взгляде.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как один день объединяет работу и посиделки?</t>
+          <t xml:space="preserve">Кузьминки соединяют ремесленный труд с молодёжным общением. Праздничный день открывает другой порядок встречи внутри сезона вечерней работы.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли народное кружево рассказывать о машине?</t>
+          <t xml:space="preserve">Трактор появляется внутри кружевного узора. Народная техника принимает машинный сюжет — традиционное ремесло рассказывает о новой эпохе.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как рисунок рассчитан на ношение?</t>
+          <t xml:space="preserve">Букет павловопосадского платка остаётся виден в складках. Композиция рассчитана на ношение: квадрат ткани работает в объёмном движении.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как материал соединяет лёгкость и укрытие?</t>
+          <t xml:space="preserve">Тонкая пуховая нить собирается в оренбургский платок. Лёгкость вещи связана с материалом и вязанием, которые можно рассмотреть вблизи.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как тяжёлый материал сохраняет тонкие детали?</t>
+          <t xml:space="preserve">Каслинское литьё передаёт тонкие детали в тяжёлом металле. Видимая лёгкость формы требует точной работы на разных этапах изготовления.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда рисунок попадает на тёмную основу?</t>
+          <t xml:space="preserve">Тёмный тагильский поднос становится цветочным полем. Роспись меняет восприятие металла, сохраняя форму вещи для повседневного использования.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сохранить прочность вокруг тонких отверстий?</t>
+          <t xml:space="preserve">Шемогодский узор прорезан в бересте насквозь. Тонкие перемычки удерживают ажур целым — красота зависит от сохранённой прочности материала.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что здесь сделал мастер, а что выросло само?</t>
+          <t xml:space="preserve">Вятский кап приносит природный рисунок ещё до обработки. Мастер выбирает форму, в которой выросшая структура дерева становится видимой.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ажурная деталь складывается в цельную вещь?</t>
+          <t xml:space="preserve">Холмогорская резьба складывает ажур из маленьких просветов. Отдельная костяная деталь требует точного соединения с остальными частями вещи.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли узнать занятие человека по маленькой фигуре?</t>
+          <t xml:space="preserve">Тобольская миниатюра передаёт занятие человека в малом масштабе. Жест и рабочий предмет помогают прочитать сцену без длинного пояснения.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как округлый рельеф создаёт игру света?</t>
+          <t xml:space="preserve">Листья кудринской резьбы выступают над поверхностью дерева. Округлый рельеф меняет свет и тень, когда взгляд смещается вокруг вещи.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рисунок должен учитывать ручку и край?</t>
+          <t xml:space="preserve">Роспись дулёвской чашки учитывает ручку и край. Цветок попадает на предмет, которым пользуются, — художественная композиция встречается с формой посуды.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где заканчивается ёмкость и начинается фигурный декор?</t>
+          <t xml:space="preserve">Скопинский сосуд соединяет ёмкость с фигурным декором. Среди затейливых деталей остаются горло, ручка и рабочее устройство посуды.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем интересен промысел, о котором редко слышат?</t>
+          <t xml:space="preserve">Судогодская игрушка сохраняет местный почерк в маленькой форме. Сравнение близких вещей помогает заметить отличия, которые теряются за общим словом «промысел».</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как перестать воспринимать промысел как безымянное производство?</t>
+          <t xml:space="preserve">Подпись возвращает узору имя мастера. Народное ремесло состоит из труда конкретных людей — знакомый рисунок не возникает сам по себе.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что начинающий ещё не умеет делать автоматически?</t>
+          <t xml:space="preserve">Ученическая ошибка показывает ещё не освоенный приём. Сравнение работ делает видимым путь руки от первой попытки к уверенной точности мастера.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему вечерний труд легче представить с другими людьми?</t>
+          <t xml:space="preserve">На посиделках трудятся и разговаривают вместе. Вечерняя работа становится местом общения, где передаются песни, рассказы и повседневный опыт.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему длинная шуба подходит не для всякого дела?</t>
+          <t xml:space="preserve">Полушубок оставляет больше свободы для работы, чем длинная верхняя одежда. Длина вещи связана с движением человека в зимнем хозяйстве.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как форма связана с работой на морозе?</t>
+          <t xml:space="preserve">Рукавица собирает пальцы в общем пространстве. Материал и следы износа помогают увидеть, как одежда служила рукам на морозе.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что наматывали на ногу перед выходом?</t>
+          <t xml:space="preserve">Онучи входят в обувной комплект раньше лаптя. Несколько слоёв работают вместе — повседневная обувь начинается с подготовки самой ноги.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в народном описании появляются сани?</t>
+          <t xml:space="preserve">В народных описаниях Введения появляется зимний выезд. Сани связывают праздничную встречу с дорогой, которая стала доступна по снегу.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочие сани выглядят иначе, чем прогулочные?</t>
+          <t xml:space="preserve">Розвальни расширяют место для хозяйственного груза. Рабочие сани отличаются от прогулочных потому, что служат другому содержимому и делу.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как уложить длинные поленья на короткую основу?</t>
+          <t xml:space="preserve">Дровни везут длинный груз на короткой основе. Укладка связывает устройство саней с будущим запасом тепла для дома.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему поленья не просто сваливают у стены?</t>
+          <t xml:space="preserve">Поленья складывают в поленницу, а не только собирают в кучу. Порядок укладки превращает множество отдельных кусков дерева в устроенный запас.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда устье печи закрывают?</t>
+          <t xml:space="preserve">Печной заслон закрывает устье большого очага. Небольшая съёмная деталь имеет своё место в устройстве, вокруг которого организован домашний труд.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему Юрьев день стал поговоркой?</t>
+          <t xml:space="preserve">Юрьев день остался в известной поговорке. Народное выражение хранит след исторической перемены, который требует отдельного объяснения событий.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно узнать о быте по углублению в стенке?</t>
+          <t xml:space="preserve">В стенке печи устроены маленькие ниши-печурки. Небольшая деталь показывает, как домашний быт использует пространство рядом с большим очагом.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как получить ещё одно место в небольшой избе?</t>
+          <t xml:space="preserve">Полати добавляют верхний ярус в небольшую избу. Домашнее пространство растёт по высоте, когда привычной площади пола недостаточно.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему кухонные вещи собраны в одном месте?</t>
+          <t xml:space="preserve">Бабий кут собирает предметы кухонной работы рядом. Часть комнаты организована последовательностью дел, которые каждый день повторяются в доме.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли судить о человеке по одной дорогой вещи?</t>
+          <t xml:space="preserve">Дорогая шуба на снимке видна сразу, жизнь её владельца — нет. Материал одежды даёт наблюдение, но достаток требует сведений о самом человеке.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие вещи хозяин держал отдельно от повседневных?</t>
+          <t xml:space="preserve">Шкатулка отделяет личные вещи от повседневного имущества. Внутренние отделения сохраняют порядок хранения, а подлинная опись возвращает содержимому имена.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как изображение и подпись работают вместе?</t>
+          <t xml:space="preserve">Лубок соединяет изображение с подписью. Рассказ разворачивается между видимым эпизодом и прочитанной строкой — взгляд и слово работают вместе.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда текст звучит для всей комнаты?</t>
+          <t xml:space="preserve">Одну книгу читают вслух нескольким людям. Домашний текст становится общей встречей: слушатели разделяют время и голос читающего.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рассказчики не повторяют текст слово в слово?</t>
+          <t xml:space="preserve">Одна сказка живёт в разных записях. Рассказчики сохраняют узнаваемые события, но меняют слова и детали — устная традиция не повторяет страницу механически.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли назвать предмет, если о нём говорят обходно?</t>
+          <t xml:space="preserve">Загадка описывает знакомую вещь обходным путём. Образное сравнение скрывает предмет и одновременно даёт признаки, по которым его можно узнать.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем зимний Никола отличается от вешнего в народном быту?</t>
+          <t xml:space="preserve">Никола зимний и вешний входят в разные сезоны быта. Память об одном святом соединяется с разными хозяйственными обстоятельствами года.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему пословица понятна не в каждом случае?</t>
+          <t xml:space="preserve">Пословица раскрывается в подходящей жизненной ситуации. Короткая фраза переносит опыт, но её смысл нельзя одинаково приложить к любому случаю.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличают людей с одинаковыми именами?</t>
+          <t xml:space="preserve">Домашнее прозвище различает людей с одинаковыми именами. Внутри сообщества имя получает дополнительную семейную историю и местный смысл.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздничный репертуар отличается от лирического?</t>
+          <t xml:space="preserve">Зимний репертуар Лопатней продолжает годовой круг села. Назначение песни слышно через её связь с конкретным праздником и исполнением.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как записать умение, которое раньше показывали руками?</t>
+          <t xml:space="preserve">В семейном рецепте мера может быть записана «на глаз». Тетрадь сохраняет слова, а комментарий владельца помогает понять переданное руками умение.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли починить вещь, повторив её структуру?</t>
+          <t xml:space="preserve">Штопка восстанавливает переплетение внутри отверстия. Ремонт повторяет устройство ткани — повреждённая вещь получает ещё время службы.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что о дарителе рассказывает собственноручная отделка?</t>
+          <t xml:space="preserve">Собственноручная упаковка показывает заботу до открытия подарка. Внешняя отделка становится частью личного обращения к тому, кому предназначена вещь.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как простое повторение превращается в украшение комнаты?</t>
+          <t xml:space="preserve">Бумажная гирлянда растёт из повторённых элементов. Простая ручная работа собирает семью вокруг подготовки общего праздничного пространства.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем длинное украшение отличается от отдельной игрушки?</t>
+          <t xml:space="preserve">Стеклянные бусы проходят линией по нескольким веткам. Длинное украшение связывает части ёлки в общий рисунок, которого не даёт одна игрушка.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ребёнок превращается в персонажа?</t>
+          <t xml:space="preserve">Новогодняя маска помогает ребёнку войти в роль. Домашний праздник получает персонажа благодаря небольшой вещи, меняющей узнаваемое лицо.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно сшить из доступных домашних материалов?</t>
+          <t xml:space="preserve">Костюм для утренника собирают из доступных материалов. За детским праздничным образом остаётся семейная работа выбора, кроя и отделки.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как мастер сохраняет навык, меняя назначение изделия?</t>
+          <t xml:space="preserve">Современный мастер меняет назначение вещи и сохраняет старый приём. Традиция продолжается через освоенное действие, которому находится новая работа.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие предметы расскажут о прожитом годе без длинной хроники?</t>
+          <t xml:space="preserve">Двенадцать вещей складываются в личный рассказ о годе. Выбранные истории соединяют сезоны, людей и труд без необходимости пересказывать всё подряд.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одна деревянная доска — а узором можно покрыть целый сарафан. Как?</t>
+          <t xml:space="preserve">Одна резная доска оставляет узор снова и снова. Набойка превращает небольшой деревянный рисунок в ткань для целого наряда.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Десятки деревянных палочек — как не запутать нити?</t>
+          <t xml:space="preserve">Десятки коклюшек движутся в руках кружевницы. Каждая держит свою нить, а порядок перекрещиваний превращает их в лёгкий ажур.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему эту одежду узнают по клетке — и почему она не похожа на сарафан?</t>
+          <t xml:space="preserve">Клетчатая понёва из Парахина устроена иначе, чем сарафан. За рисунком ткани открывается крой конкретной вещи и мастерство местной традиции.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем в женском головном уборе твёрдые рога?</t>
+          <t xml:space="preserve">Под нарядным верхом кички скрыты твёрдые рога. Необычный силуэт создаётся из нескольких частей и связан с убором замужней женщины.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как шить двумя руками, если ткань всё время приходится держать?</t>
+          <t xml:space="preserve">Деревянная швейка держит край ткани, пока руки ведут шов. Небольшая помощница берёт на себя ту работу, для которой не хватает третьей руки.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему колыбель висит, а не стоит на полу?</t>
+          <t xml:space="preserve">Колыбель висит над полом. Подвес меняет движение детской постели — устройство домашней вещи становится частью заботы о ребёнке.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ни мотора, ни батарейки. Кто заставляет кузнецов стучать молотками?</t>
+          <t xml:space="preserve">Ни мотора, ни батарейки — кузнецы стучат молотками. Движение деревянных планок оживляет игрушку, вырезанную мастером.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крана нет. Как вымыть руки и не вылить сразу всю воду?</t>
+          <t xml:space="preserve">У рукомойника нет крана, но воду можно выпускать понемногу. Простая форма помогает вымыть руки, не опорожняя весь запас за один раз.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему два ведра могли быть удобнее одного?</t>
+          <t xml:space="preserve">Два ведра висят по сторонам коромысла. Нагрузка распределяется между ними — знакомый предмет превращает тяжёлую ношу в продуманную систему.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дощечки прижаты обручами — почему эта кадушка подходит для теста?</t>
+          <t xml:space="preserve">Дощечки квашни стянуты обручами. Ёмкость собирается из отдельных частей и служит месту, где замешивают и оставляют подниматься тесто.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">У чаши широкий бок и слив. Как из неё угощали целую компанию?</t>
+          <t xml:space="preserve">Широкая чаша и носик помогают разливать угощение. Форма сосуда хранит порядок общей трапезы — вещь сделана для встречи людей.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Этой кадушкой пользовалась одна семья больше полувека. Что происходило внутри?</t>
+          <t xml:space="preserve">Одной маслобойкой семья пользовалась больше полувека. За деревянными стенками привычным движением превращали сливки в масло.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар положили на чашу. Что должно появиться на другой стороне?</t>
+          <t xml:space="preserve">Товар лежит на одной чаше, гири — на другой. Равновесие делает меру видимой обоим участникам торговли, ещё до появления цифры на экране.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Урожай собран. Почему за него всё ещё тревожились зимой?</t>
+          <t xml:space="preserve">Урожай уже собран, а забота о нём продолжается зимой. Хранение запасов требует труда не меньше, чем праздничная благодарность за плоды.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как церковная встреча стала в народном календаре встречей зимы с весной?</t>
+          <t xml:space="preserve">Сретение означает встречу, а народный календарь связывает день со встречей зимы и весны. Церковный смысл и сезонный образ живут рядом.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем вырезать рыб на доске, с которой получается огромный пряник?</t>
+          <t xml:space="preserve">Рыбы вырезаны в дереве, чтобы появиться на прянике. Доска хранит рисунок большого угощения — съедобный рельеф начинается с работы резчика.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ленты, иголки, пуговицы — как целая лавка помещалась на плечах?</t>
+          <t xml:space="preserve">Ленты, иголки и пуговицы умещаются в переносной лавке. Коробейник несёт товар на себе и связывает торговлю с дорогой между поселениями.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему на столе столько мучного и молочного?</t>
+          <t xml:space="preserve">На столе мучное и молочное. Масленичное угощение принадлежит определённому месту в годовом круге — сам праздник меняет дату каждый год.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как катание с горки связывали с будущим урожаем?</t>
+          <t xml:space="preserve">Катание с горки связывали с будущим урожаем. Зимняя забава хранит народное пожелание благополучия, а не способ управлять полем.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто кому приходится роднёй — и к кому идут молодые супруги?</t>
+          <t xml:space="preserve">Молодые супруги входят в новую сеть родства. Праздничные визиты делают эту связь зримой: у каждого родственника своё место во встрече.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему уличная кукла могла говорить со зрителями так бойко?</t>
+          <t xml:space="preserve">Маленькая уличная кукла бойко отвечает зрителям. За голосом и движением Петрушки стоит артист, умеющий превратить толпу в собеседника.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лошадей ещё не видно, а об их приближении уже знают. Откуда идёт звон?</t>
+          <t xml:space="preserve">Лошадей ещё не видно, а звон уже слышен. Поддужный колокольчик делает приближение упряжки слышимым раньше, чем она покажется на дороге.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем крестьянин оставил своё имя на дуге?</t>
+          <t xml:space="preserve">На расписной дуге осталось имя хозяина. Рабочая часть упряжи хранит личный след человека — надпись пережила привычную дорогу.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему благополучию скота посвящали особый день?</t>
+          <t xml:space="preserve">Благополучию скота посвящали особый день. Народный календарь сохраняет прямую связь семейной жизни с животными, от которых зависел достаток.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Озеро подо льдом — зачем сейчас работать над летними снастями?</t>
+          <t xml:space="preserve">Озеро подо льдом, а руки готовят снасти к открытой воде. Рыбацкий год продолжается зимой: будущий выход начинается за домашней работой.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему местным рыбакам зимой мешала дешёвая привозная рыба?</t>
+          <t xml:space="preserve">Привозная рыба меняет жизнь местного промысла. За ценой на зимнем рынке стоят дорога, сезон и труд людей, ловивших рядом с домом.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что мастер называет кокорой — и где её искать в лодке?</t>
+          <t xml:space="preserve">Кокора использует естественный изгиб дерева. В лодке природная форма становится конструктивной деталью — мастерство начинается с выбора заготовки.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ремесло становится личным открытием человека нашего времени?</t>
+          <t xml:space="preserve">Человек нашего времени осваивает старое ремесло руками. Между музейной вещью и личным опытом появляется связь через освоенное движение.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли из обрезков сшить вещь, которую будут беречь десятилетиями?</t>
+          <t xml:space="preserve">Лоскуты, оставшиеся от разных тканей, собираются в одеяло. Маленькие обрезки получают вторую жизнь — узор держится на терпении и точности шва.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем бить стебли деревянной лопаткой, если из них хотят получить мягкую ткань?</t>
+          <t xml:space="preserve">Льняные стебли бьют деревянной трепалкой, чтобы отделить лишнее. Мягкость будущего полотна начинается с тяжёлой и совсем не мягкой работы.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как из одного пучка получались и грубая верёвка, и тонкое полотно?</t>
+          <t xml:space="preserve">Из пучка льна выделяют волокно разного качества. Чесание разделяет будущие нити: материал для грубой работы и тонкого полотна готовят по-разному.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как хозяйка понимала, хватит ли пряжи на целый холст?</t>
+          <t xml:space="preserve">Пряжу считают и сматывают до начала ткачества. Будущий холст ещё не виден, но его размер уже требует точного домашнего расчёта.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нога нажала — между сотнями нитей появилась дорога. Как?</t>
+          <t xml:space="preserve">Нога нажимает подножку — между нитями открывается проход. Ткацкий стан переводит движение тела в порядок переплетения будущего холста.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему ткацкий инструмент похож на маленькую лодку?</t>
+          <t xml:space="preserve">Челнок похож на лодку и несёт нить сквозь основу. Каждый проход оставляет новый ряд ткани — маленький инструмент работает на ширину полотна.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Увидел фабричную машину — и вырезал свою. Разве так можно?</t>
+          <t xml:space="preserve">Увиденную машину мастер воспроизводит в дереве. Самодельное устройство хранит попытку понять чужой механизм и заставить его работать своими руками.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что превращает массовую открытку в обращение к одному человеку?</t>
+          <t xml:space="preserve">Открытку печатают для тысяч людей, а подпись адресуют одному. Несколько рукописных строк превращают массовую картинку в личное обращение.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем утюгу отверстия, если гладить должна его подошва?</t>
+          <t xml:space="preserve">Угольному утюгу нужен воздух: отверстия поддерживают жар внутри. Гладкая подошва скрывает маленькую топку, которую приходилось обслуживать.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему нарядное полотенце берегли для событий, а не только для умывания?</t>
+          <t xml:space="preserve">Нарядное полотенце берегут для важных встреч и обрядов. Вышитая ткань участвует в событии, сохраняя больше смысла, чем обычная вещь для умывания.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где у деревянной утки спряталась крышка?</t>
+          <t xml:space="preserve">Деревянная утка скрывает вместилище под крышкой. Скульптурная форма соединяет узнаваемую птицу с практической домашней вещью.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как берёзовая кора превращается в посуду для питья?</t>
+          <t xml:space="preserve">Берёзовая кора становится сосудом для питья. В туесе природный материал получает форму посуды — соединения важны не меньше рисунка поверхности.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у этого молочного сосуда нет ручки?</t>
+          <t xml:space="preserve">Молочный сосуд без ручки приходится брать за корпус. Форма привычной посуды направляет движение рук и хранит опыт ежедневного обращения.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему один день зовут и Свистуньей, и Весновкой, и Плющихой?</t>
+          <t xml:space="preserve">Один день зовут Свистуньей, Весновкой и Плющихой. Народные названия сохраняют разные наблюдения за весной, а не единый прогноз погоды.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что делали со ступой в настоящем доме, пока Баба-яга летала в сказке?</t>
+          <t xml:space="preserve">В сказке ступа летает, в доме помогает обрабатывать зерно. Тяжёлый пест возвращает знакомому образу его настоящее рабочее назначение.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куда исчезает зерно, которое насыпали в середину?</t>
+          <t xml:space="preserve">Зерно уходит между жерновами и выходит размолотым. Движение двух камней превращает запас урожая в основу будущей еды.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как прилёт грачей превращался в событие всей деревни?</t>
+          <t xml:space="preserve">Прилёт грачей становился заметным событием весны. Народный календарь сохраняет внимание к живой природе, от которой зависел годовой труд.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему одной сеткой нельзя одинаково просеять всё?</t>
+          <t xml:space="preserve">Мука и крупа требуют разного сита. Размер отверстий решает, что останется сверху, а что пройдёт сквозь сетку в другую посуду.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как учиться письму, если новая страница не нужна?</t>
+          <t xml:space="preserve">На грифельной доске пишут, стирают и пишут снова. Один предмет даёт ученику множество новых попыток без новой бумажной страницы.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем держать один нож сразу двумя руками?</t>
+          <t xml:space="preserve">Скобель держат двумя руками и тянут на себя. Лезвие снимает древесину контролируемым движением — форма будущей вещи появляется под усилием мастера.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как внутри нарядной глиняной фигуры помещается музыкальный инструмент?</t>
+          <t xml:space="preserve">Внутри глиняной фигурки скрыта полость свистульки. Нарядная игрушка становится инструментом: её голос зависит от устройства, а не только от росписи.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему весну встречали с птицей из теста в руках?</t>
+          <t xml:space="preserve">Весну встречают с птицей из теста в руках. Печёный жаворонок соединяет домашнюю работу с образом возвращения птиц и ожиданием тепла.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плоские полоски лыка огибают человеческую стопу?</t>
+          <t xml:space="preserve">Плоские полоски лыка огибают стопу и образуют обувь. Лапоть держится на порядке переплетения — материал становится объёмом без тканого полотна.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как кусок кожи превращается в обувь?</t>
+          <t xml:space="preserve">Кусок кожи получает крой, сгибы и соединения. Обувь возникает из точной работы с плоской заготовкой, которой предстоит принять форму ноги.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему от старого орудия в музее могла остаться только железная часть?</t>
+          <t xml:space="preserve">От деревянного орудия может сохраниться только железная часть. Музейный остаток требует увидеть утраченную рукоять и работу целого предмета.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем ребёнку уменьшенная копия сельского орудия?</t>
+          <t xml:space="preserve">Ребёнку делают уменьшенное сельское орудие. Маленькая вещь показывает, как знакомство с трудом входило в повседневную жизнь семьи.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как пройти поле и не оставить пустую полосу?</t>
+          <t xml:space="preserve">Сеятель проходит поле и распределяет зерно рукой. Ровность будущего посева зависит от шага и размаха — точность рождается из освоенного движения.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что удерживает вместе десятки отдельных деревянных частей?</t>
+          <t xml:space="preserve">Десятки деревянных частей удерживаются соединениями. Колесо показывает, как отдельные заготовки становятся единой конструкцией под нагрузкой.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что заставляет часы идти, когда в них нет батарейки?</t>
+          <t xml:space="preserve">Часы идут без батарейки: механизм получает запас механической энергии. За циферблатом скрыта передача движения от детали к детали.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у одного дня столько водяных названий?</t>
+          <t xml:space="preserve">В народных именах весеннего дня слышится вода. Названия сохраняют сезонный опыт людей, внимательно следивших за таянием и течением.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как украсить бересту рисунком, не рисуя по ней кистью?</t>
+          <t xml:space="preserve">Бересту украшают без кисти — рисунок появляется от обработки поверхности. Узор рождается из свойств самой коры и точного движения инструмента.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Этой деревянной лопаткой не готовили еду. Что она делала у воды?</t>
+          <t xml:space="preserve">Деревянной лопаткой работают у воды, а не у плиты. Валёк помогает стирать бельё: знакомая форма скрывает другую домашнюю нагрузку.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у обыкновенной стиральной доски есть автор?</t>
+          <t xml:space="preserve">У стиральной доски есть конкретный изготовитель. Даже привычная домашняя вещь сохраняет авторство и след труда, который обычно остаётся незаметным.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как получить большую ёмкость, если нет ни досок, ни обручей?</t>
+          <t xml:space="preserve">Большую ёмкость выдалбливают из цельного дерева. Ни досок, ни обручей — стенки и дно остаются частями одной заготовки.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одним маленьким колёсиком сделать комнату светлее?</t>
+          <t xml:space="preserve">Маленькое колёсико меняет положение фитиля. Свет керосиновой лампы зависит от движения детали, которую легко не заметить рядом со стеклом.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему праздник о далёком Иерусалиме встречают с вербой?</t>
+          <t xml:space="preserve">Праздник Входа в Иерусалим встречают с вербой. Весенняя ветвь входит в русскую местную традицию праздника с далёким евангельским событием.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем украшать ту сторону деревянной формы, которую никто не видит?</t>
+          <t xml:space="preserve">Узор внутри пасочницы появится снаружи на готовой пасхе. Скрытая резьба формы работает как обратное изображение будущего праздничного блюда.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее привычной работы, если даже прялку оставляют в покое?</t>
+          <t xml:space="preserve">На Благовещение привычную работу могли откладывать. Остановленная прялка становится знаком праздничного времени в народном домашнем укладе.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли маленький подарок рассказать, кто и кому его поднёс?</t>
+          <t xml:space="preserve">Маленький пасхальный подарок хранит адресное обращение. Надпись и отделка помогают увидеть за вещью человека, который выбирал её для другого.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как выиграть пасхальное яйцо, не разбивая его?</t>
+          <t xml:space="preserve">Пасхальное яйцо можно выиграть катанием. Праздничная игра требует рассчитать путь целой хрупкой вещи, не превращая встречу в бой скорлупок.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как поздравить человека, до которого нельзя дойти пешком?</t>
+          <t xml:space="preserve">Праздничная открытка проходит дорогу вместо отправителя. Подпись соединяет людей, которые не могут встретиться за одним столом.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем к чаепитию понадобились кусачки с маленьким поддоном?</t>
+          <t xml:space="preserve">Кусачки отделяют кусочек от сахарной головы. Маленький поддон у инструмента напоминает, что сладкое угощение когда-то готовили иначе.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как рассказать о духовном пути при помощи теста?</t>
+          <t xml:space="preserve">Лестница из теста становится образом духовного пути. Домашняя выпечка сохраняет символ праздника в предмете, который можно взять в руки.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куда делся кофе, если зёрна засыпали сверху?</t>
+          <t xml:space="preserve">Зёрна засыпают сверху, молотый кофе собирается внизу. Между ними работает ручной механизм — чашка начинается с усилия человека.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему тяжёлую чугунную вещь помнят по тарелке вафель?</t>
+          <t xml:space="preserve">Тяжёлую чугунную вафельницу помнят по лёгкому хрустящему угощению. Рельеф горячих створок остаётся рисунком на готовой выпечке.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как везти чернила с собой, когда ручку ещё надо обмакивать?</t>
+          <t xml:space="preserve">Чернила берут в дорогу в отдельной вещи. Походная чернильница хранит время, когда пишущий инструмент приходилось снова обмакивать.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что в названии народного дня напоминает о движении воды?</t>
+          <t xml:space="preserve">Народное имя весеннего дня напоминает о движении воды. За названием стоит наблюдение за сезонной переменой, а не точная дата ледохода.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что делали с телефоном, у которого нет привычного набора номера?</t>
+          <t xml:space="preserve">У старого телефона нет привычного набора номера. Связь начиналась с другого действия — устройство показывает перемены в повседневном общении.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как освободить руки, когда несёшь всё нужное через лес?</t>
+          <t xml:space="preserve">Кузовок освобождает руки в лесной дороге. Плетёная вещь распределяет ношу за спиной и соединяет свойства материала с движением человека.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему много деревянных пальцев делают работу быстрее одного?</t>
+          <t xml:space="preserve">Много деревянных зубьев работают одним движением. Грабли собирают рассеянное по земле — ширина инструмента превращает усилие в быстрый проход.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как передать усилие лошади повозке и распределить контакт с телом?</t>
+          <t xml:space="preserve">Хомут соединяет тело лошади с работой повозки. Форма упряжи распределяет контакт и передаёт тягу: удобство здесь связано с устройством.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему работа с деревом стала выражением о безделье?</t>
+          <t xml:space="preserve">Баклуша — деревянная заготовка, а выражение звучит как безделье. За знакомыми словами скрыт реальный этап изготовления домашней утвари.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему сапожнику нужна ещё одна нога, кроме ноги заказчика?</t>
+          <t xml:space="preserve">Сапожник работает с колодкой вместо ноги заказчика. Деревянная форма удерживает размер и объём, пока плоский материал становится обувью.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли рабочий сигнал превратиться в мелодию для гулянья?</t>
+          <t xml:space="preserve">Пастушеский рожок подаёт сигнал и звучит в музыкальном ансамбле. Рабочий инструмент получает новую жизнь в руках исполнителя.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему привычному гармонисту бывает трудно сыграть на другой гармони?</t>
+          <t xml:space="preserve">Привычные движения не всегда подходят другой гармони. Местные системы инструмента сохраняют разные способы извлекать и связывать звуки.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что должен сделать мастер, чтобы знакомый инструмент зазвучал в оркестре?</t>
+          <t xml:space="preserve">Для оркестра знакомый инструмент меняют и настраивают. Работа мастера помогает народному звучанию войти в согласованный голос большого состава.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в празднике, когда человек сам входит в хоровод?</t>
+          <t xml:space="preserve">Человек входит в хоровод и становится частью общего движения. Праздник складывается из согласованного шага, пения и внимания к соседу.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему народный хор не звучит как несколько одинаковых голосов?</t>
+          <t xml:space="preserve">Народный хор объединяет разные голоса. Общее звучание возникает из их взаимодействия — отдельная партия не обязана повторять остальные.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему детская игровая бита отлита из чугуна и украшена?</t>
+          <t xml:space="preserve">Игровая бита отлита из чугуна и украшена. Маленькая детская вещь хранит вес настоящего материала и внимание мастера к её виду.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как устроить музыкальный вечер там, где нет розетки?</t>
+          <t xml:space="preserve">Музыкальный вечер начинается без розетки. Заведённый механизм граммофона двигает пластинку — домашнее слушание имеет собственную историю труда.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли вытащить крошечную расписную вещь, не потревожив остальные?</t>
+          <t xml:space="preserve">Из расписной вещи появляется ещё одна, меньше. Матрёшка держит целую последовательность объёмов внутри формы, которая кажется одной игрушкой.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда гость переступает порог двора?</t>
+          <t xml:space="preserve">Гость и хозяин проходят одну калитку, но идут разными путями. Маленькая граница двора открывает порядок соседства и домашнего труда.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему сани нельзя просто поставить на колёса?</t>
+          <t xml:space="preserve">Телега отличается от саней не только колёсами. Летний путь требует другой опоры и размещения груза — устройство меняется вместе с дорогой.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что первым замечаешь в мужской рубахе?</t>
+          <t xml:space="preserve">Застёжка косоворотки смещена в сторону. Небольшая деталь сразу меняет вид рубахи и помогает различить крой, не придумывая единую историю его появления.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как поднять руки в рубахе из прямых полотнищ?</t>
+          <t xml:space="preserve">Небольшой лоскут под рукавом даёт свободу движения. Ластовица показывает, как точная деталь меняет удобство рубахи из прямых полотнищ.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что нужно взять человеку, который уйдёт со стадом на весь день?</t>
+          <t xml:space="preserve">Пастух уходит со стадом на целый день. Его сумка собирает нужное вдали от дома — каждый предмет занимает место ради конкретного дела.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему начало выпаса становилось событием для деревни?</t>
+          <t xml:space="preserve">Первый выход стада становится событием деревни. В обычаях Егорьева дня сезонный труд соединяется с заботой людей о благополучии хозяйства.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли услышать, где пасётся твоя корова?</t>
+          <t xml:space="preserve">Корова скрылась из виду, но ботало выдаёт её движение. Маленькая звучащая вещь помогает человеку следить за стадом на расстоянии.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как двор помогает заботиться о домашних птицах?</t>
+          <t xml:space="preserve">Для птицы во дворе отводят гнездо, корм и воду. Небольшой участок хозяйства показывает, сколько ежедневного внимания требует домашняя живность.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие следы большого события остаются в домашнем альбоме?</t>
+          <t xml:space="preserve">Большая Победа остаётся в семейном альбоме. Снимок сохраняет лица, а подписи и воспоминания возвращают имена людей и обстоятельства встречи.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как прямоугольные полотнища становятся просторной одеждой?</t>
+          <t xml:space="preserve">Прямоугольные полотнища собираются в просторный сарафан. Объём рождается из сборки ткани — сложный силуэт начинается с простых частей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли расширить подол, сохранив узкий верх?</t>
+          <t xml:space="preserve">Клинья расширяют подол, оставляя верх узким. В косоклинном сарафане мастерство кроя видно по тому, как распределяется ткань в движении.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как многослойность меняет весь костюм?</t>
+          <t xml:space="preserve">Короткая душегрея меняет вид длинного сарафана. Костюм складывается слоями: одна вещь задаёт новый силуэт всему наряду.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочая вещь могла стать нарядной?</t>
+          <t xml:space="preserve">Передник защищает одежду и несёт отделку. Рабочая вещь может стать нарядной — местная традиция соединяет пользу с вниманием к красоте.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая деталь меняет причёску?</t>
+          <t xml:space="preserve">Косник держится на конце девичьей косы. Маленькое украшение рассчитано на конкретное место: крепление объясняет форму не хуже узора.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что скрывается за одним названием?</t>
+          <t xml:space="preserve">За названием «сорока» скрывается убор из нескольких частей. Каждый слой делает свою работу, прежде чем появится знакомый нарядный силуэт.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему украшение интересно рассматривать не только спереди?</t>
+          <t xml:space="preserve">Подвесы нагрудного украшения видны сбоку и в движении. Наряд устроен объёмно: способ крепления хранит часть мастерского замысла.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как покупной материал меняет привычную рубаху?</t>
+          <t xml:space="preserve">Покупной кумач входит в деревенскую одежду. Новый материал меняет поверхность привычной рубахи, сохраняя связь обновления с местным костюмом.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какая ткань выдавала стремление одеться модно?</t>
+          <t xml:space="preserve">Плис придаёт нарядным штанам особую поверхность. Молодёжная мода читается в фактуре ткани, которую трудно заметить издали.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В какой момент городской силуэт становится деревенским?</t>
+          <t xml:space="preserve">Кофта и юбка составляют «парочку». Новый силуэт входит в местный гардероб — история деревенской одежды продолжается через перемены кроя.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли один платок выглядеть как три разные вещи?</t>
+          <t xml:space="preserve">Один квадратный платок можно сложить и надеть по-разному. Движение рук меняет силуэт вещи без единого нового шва.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему этот день нельзя навсегда поставить на 21 мая?</t>
+          <t xml:space="preserve">Вознесение зависит от даты Пасхи и не закреплено за одним числом мая. Подвижный праздник показывает другой способ устроить годовой круг.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одна память соединяла разные занятия людей?</t>
+          <t xml:space="preserve">Никола вешний входит в хозяйственный календарь разных мест. Один праздничный день связывает церковную память с конкретными занятиями людей.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что рассказывает подошва о работе мастера?</t>
+          <t xml:space="preserve">Подошва прячет работу сапожника от первого взгляда. Гвозди и швы показывают, каким способом мастер удержал вместе части обуви.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как научиться читать, если книг совсем немного?</t>
+          <t xml:space="preserve">Домашняя азбука превращает буквы в освоенное умение. Одна страница хранит путь от узнавания знака к слову, которое ребёнок читает сам.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли понять работу замка, не сломав его?</t>
+          <t xml:space="preserve">Поворот ключа двигает скрытый запор. Медный замок соединяет небольшое движение руки с защитой вещей, которым хозяин отвёл особое место.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что держит створку годами?</t>
+          <t xml:space="preserve">Тяжёлая дверь держится на кованых петлях. Длинная металлическая полоса распределяет крепление — кузнечная работа остаётся в ежедневном движении створки.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая скамья становится местом общения?</t>
+          <t xml:space="preserve">Лавка у дома собирает соседей. Простая скамья становится местом обмена новостями, когда люди задерживаются рядом и обращаются друг к другу.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему берёза появляется в рассказах о начале лета?</t>
+          <t xml:space="preserve">Берёзовые ветви входят в семицкий обряд. Зелёный материал становится частью праздничного действия, порядок которого различается от места к месту.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько изгибов превращаются в бегущую лошадь?</t>
+          <t xml:space="preserve">Несколько изгибов кисти создают городецкого коня. Движение животного читается в силуэте ещё до появления мелких деталей нарядной росписи.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли продолжить узор, не зная его названия?</t>
+          <t xml:space="preserve">Красный и чёрный складываются в повторяющийся ряд. Мезенская роспись держит ритм узора: следующий элемент связан с уже написанными.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в знакомом интерьере в праздничный день?</t>
+          <t xml:space="preserve">На Троицу привычный дом получает зелёное убранство. Местный обычай делает праздник видимым внутри повседневного семейного пространства.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли сделать упругую игрушку без резины?</t>
+          <t xml:space="preserve">Тряпичный мяч обходится без резины. Домашние материалы собираются в игрушку — игра начинается с умения придать форму тому, что под рукой.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в народном календаре могли откладывать работу с землёй?</t>
+          <t xml:space="preserve">В народном представлении земля бывает именинницей. Отложенная работа в Духов день показывает обрядовую паузу внутри непрерывного сельского труда.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как июньский посев связан с зимней рубахой?</t>
+          <t xml:space="preserve">Имя Олёны-льняницы связывает посев с будущим полотном. Между летним полем и зимней рубахой лежит длинная цепь человеческой работы.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее в этой игре — скорость или внимание?</t>
+          <t xml:space="preserve">В горелках пара разбегается, а водящему надо успеть отреагировать. Скорость работает вместе с вниманием к моменту начала движения.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда выгоднее бежать, а когда ждать?</t>
+          <t xml:space="preserve">В лапте удар открывает время для перебежки. Игрок соотносит свой старт с действиями соперников — командная игра требует общего расчёта.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одна и та же пятёрка создаёт разные задачи?</t>
+          <t xml:space="preserve">Пять чурок складываются в разные фигуры городков. Материал остаётся прежним, но новое расположение меняет задачу для каждого броска.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем участники заранее договариваются о границах?</t>
+          <t xml:space="preserve">Граница площадки меняет игру в салочки. Договорённость участников становится действующим правилом, без которого один и тот же бег означает разное.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ритм помогает группе принять решение?</t>
+          <t xml:space="preserve">Считалка распределяет слоги между участниками и выбирает водящего. Ритм помогает группе начать игру с общего принятого порядка.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли игрушка сохранить подробности взрослого наряда?</t>
+          <t xml:space="preserve">Наряд самодельной куклы умещается в ладони. Игрушка способна сохранить детали взрослого местного костюма в масштабе детской игры.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как услышать момент для движения?</t>
+          <t xml:space="preserve">В Тимоне движение ног связано с наигрышем. Музыкальная опора становится телесным ритмом — услышанное продолжается в шаге танцующего.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как участники сохраняют общее движение?</t>
+          <t xml:space="preserve">Карагод держится на согласованном движении людей. Общий круг складывается из отдельных шагов, которые участники соотносят друг с другом.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто ведёт, а кто отвечает?</t>
+          <t xml:space="preserve">Инструменты плясового ансамбля вступают в разное время. В общем звучании слышны ведущие и ответные движения музыкальной фразы.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли рабочее дело иметь свой напев?</t>
+          <t xml:space="preserve">В Фощеватове песня сопровождает полотьё. Напев сохраняет связь с конкретным сезонным делом, а не только с праздничным выступлением.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему соседние песни звучат так по-разному?</t>
+          <t xml:space="preserve">В одном селе Лопатни живут песни разных слоёв репертуара. Соседство старого и нового показывает традицию, которая продолжает меняться.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где заканчивается строка, если мелодия ещё продолжается?</t>
+          <t xml:space="preserve">В песнях Осереди слово может закончиться раньше распева. Длинная музыкальная фраза раскрывает время, которое голос даёт одной строке.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ворот меняет усилие человека?</t>
+          <t xml:space="preserve">Рукоять колодезного ворота поднимает ведро из глубины. Поворот руки превращается в вертикальное движение тяжёлого запаса воды.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как распределить небольшой участок между разными культурами?</t>
+          <t xml:space="preserve">Огород рядом с домом делят между разными культурами. За небольшими грядами стоит сезонный порядок ухода и будущего семейного стола.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему старый рассказ о репке понятен через хозяйство?</t>
+          <t xml:space="preserve">Репа возвращает знакомую сказку в хозяйственный мир. За большой сказочной работой стоит настоящий овощ и его место в домашней еде.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что в летней еде нельзя повторить зимой без запасов?</t>
+          <t xml:space="preserve">Сезонная зелень меняет состав обеда. Щавель показывает, как стол связан с появлением свежих растений, а не только с зимним запасом.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что видно над водой и что происходит под ней?</t>
+          <t xml:space="preserve">Поплавок остаётся на поверхности и передаёт движение снасти. Маленькая вещь делает видимым то, что происходит под водой.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему названия дней хранят внимание к погоде?</t>
+          <t xml:space="preserve">Народный календарь сохраняет наблюдения за летней погодой. Имя Фёдора Стратилата становится точкой сезонной памяти, а не гарантией прогноза.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плетёная ловушка удерживает добычу?</t>
+          <t xml:space="preserve">У мережи вход устроен иначе, чем выход. Форма рыболовной снасти направляет движение — результат зависит от конструкции целого предмета.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем лодочнику сосуд, которым ничего не пьют?</t>
+          <t xml:space="preserve">Черпак убирает воду со дна лодки. Простая ручная вещь напоминает, что работа на воде включает постоянную заботу о самом судне.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какая часть узора одновременно решает бытовую задачу?</t>
+          <t xml:space="preserve">Наличник украшает окно и закрывает стык. Красота резной детали соединена с устройством дома: узор занимает место конкретной строительной части.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется дом, когда ставни закрывают?</t>
+          <t xml:space="preserve">Ставни дают окну дополнительное закрытие. Створки меняют вид фасада и повседневное обращение с границей между комнатой и улицей.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличить гречиху от привычного хлебного колоса?</t>
+          <t xml:space="preserve">Гречиха вошла в народное имя Акулинина дня. Календарное название связывает растение с сезонным вниманием людей к будущему урожаю.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему крупа не похожа на длинное зерно ржи?</t>
+          <t xml:space="preserve">У гречневого зерна характерная трёхгранная форма. Знакомая крупа возвращает взгляд от тарелки к растению и обработке урожая.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как цветы удерживают композицию на круглом подносе?</t>
+          <t xml:space="preserve">Листья жостовской росписи собираются веерными движениями кисти. Растительный мотив держится на порядке мазков, а не на обводке готового контура.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как узнать игрушку ещё до раскраски?</t>
+          <t xml:space="preserve">Филимоновская свистулька вытягивает силуэт в глине. Местный почерк виден ещё до росписи — форму и звучание мастер создаёт вместе.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что человек выбирает рассказать близким прежде всего?</t>
+          <t xml:space="preserve">Летние новости укладываются на одном листе. Домашнее письмо сохраняет личный голос человека, которому предстояло преодолеть расстояние словами.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему не всякой косой работают одинаково?</t>
+          <t xml:space="preserve">Изгиб косы-горбуши подсказывает движение косаря. Форма инструмента связана с работой тела, а не только с остротой металлического края.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, если рукоять слишком длинна?</t>
+          <t xml:space="preserve">Косовище подгоняют под человека. Деревянная рукоять соединяет рост, хват и движение — удобство рождается из точного соответствия работнику.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему работа в поле прерывается короткими остановками?</t>
+          <t xml:space="preserve">Брусок возвращает косе рабочую остроту. Покос требует заботы об инструменте: остановка для правки становится частью непрерывного труда.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как устроить жизнь, когда рабочее место далеко от дома?</t>
+          <t xml:space="preserve">На долгий покос берут больше одной косы. Еда, одежда и рабочие вещи собирают повседневную жизнь там, где семье предстоит провести несколько дней.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему скошенную траву не сразу уносят под крышу?</t>
+          <t xml:space="preserve">Скошенная трава ещё не стала зимним запасом. Просушка требует времени и внимания — поспешность может перечеркнуть тяжёлую работу покоса.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у летнего дня такое имя?</t>
+          <t xml:space="preserve">Банный обычай входит в день Аграфены Купальницы. Подготовка тела и домашние действия соединяются с местным порядком летнего праздника.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличить народное предание от свойства растения?</t>
+          <t xml:space="preserve">Купальский рассказ обещает чудесный цветок. Предание открывает народное воображение и ожидание необычного, сохраняя отличие от ботанического факта.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли разобраться в большой семье по одному рассказу?</t>
+          <t xml:space="preserve">За семейным столом видна сеть родства. Один человек оказывается для соседей сыном, супругом или дядей — связь зависит от точки отсчёта.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как разместить много лёгкого, но объёмного груза?</t>
+          <t xml:space="preserve">Сено хранят над хозяйственным двором. Запас занимает верхний ярус дома и связывает устройство постройки с годовым ритмом ухода за животными.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько людей работают без одинаковых заданий?</t>
+          <t xml:space="preserve">Артель делит большое дело между людьми. Общий результат складывается из разных ролей, согласованности действий и принятого порядка работы.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как накормить семью, когда все далеко от печи?</t>
+          <t xml:space="preserve">Полевой обед должен добраться до работников. Сосуды и переноска становятся частью питания — домашняя еда получает собственный маршрут.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает праздник и начало сенокоса в Кижах?</t>
+          <t xml:space="preserve">Петров день отмечает перемену летнего хозяйственного ритма. Праздник включён в местный год работ, который не сводится к одной общей схеме.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему два сильных гребца могут мешать друг другу?</t>
+          <t xml:space="preserve">Два весла должны работать согласованно. Направление лодки зависит от соотношения движений — совместное усилие требует общего ритма.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что может служить якорем без сложной металлической формы?</t>
+          <t xml:space="preserve">Тяжёлый камень удерживает лодку через привязанную снасть. Природный материал получает новое назначение в продуманном рыбацком устройстве.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как вещь из села становится музейным свидетельством?</t>
+          <t xml:space="preserve">Коллекция Ольги Семёновой начинается со встреч с людьми и вещами. За музейным собранием стоит личная работа узнавания и сохранения.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему название вещи без места и имени почти бесполезно?</t>
+          <t xml:space="preserve">Полевой блокнот удерживает то, что легко забыть после встречи. Имя, место и обстоятельства записи помогают вещи сохранить человеческий контекст.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как восстановить одну ячейку, не переделывая всё полотно?</t>
+          <t xml:space="preserve">Рыбацкая игла проводит нить через ячейки сети. Починка возвращает снасти рабочую форму — добыча начинается с терпеливого ручного ремонта.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как переносная ёмкость связана со средой рыбака?</t>
+          <t xml:space="preserve">Садок оставляет пойманную рыбу в воде. Устройство продолжает работу рыбака после ловли, удерживая улов в отдельном пространстве.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у человека рядом с ульем появляется дым?</t>
+          <t xml:space="preserve">Дымарь входит в набор пасечника. Форма прибора и направленный выход дыма показывают, как инструмент подчинён конкретной работе с ульем.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как природная форма превращается в хозяйственную вещь?</t>
+          <t xml:space="preserve">Ствол дерева становится ульем-колодой. Человек использует природную форму, превращая её в часть устроенного пчелиного хозяйства.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда часть улья становится съёмной?</t>
+          <t xml:space="preserve">Рамку можно вынуть из улья отдельно. Съёмная деталь меняет доступ к внутреннему устройству — работа пасечника получает новую возможность.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько слабых полос становятся одним креплением?</t>
+          <t xml:space="preserve">Тонкое лыко собирается в прочную верёвку. Скручивание связывает отдельные волокна: запас прочности рождается из их совместной работы.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где нужна ткань, которую не наденешь на праздник?</t>
+          <t xml:space="preserve">Грубая рогожа тоже требует ткацкого умения. Польза прочного полотна держится на порядке переплетения, даже когда вещь не называют нарядной.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему деревянная вещь выглядит металлической?</t>
+          <t xml:space="preserve">Хохломская ложка сияет золотым цветом, оставаясь деревянной. Отделка меняет вид материала — мастерство скрыто под знакомым праздничным блеском.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как кисть получает свет и тень без смены краски?</t>
+          <t xml:space="preserve">Один синий цвет даёт множество оттенков гжельского мазка. Нажим и движение кисти превращают ограниченную палитру в объёмный рисунок.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему узор легко узнать издалека?</t>
+          <t xml:space="preserve">Круги и полосы становятся нарядом дымковской барышни. Простой элемент работает вместе с формой фигурки и ритмом всей росписи.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто этот персонаж между человеком и конём?</t>
+          <t xml:space="preserve">Каргопольский Полкан соединяет необычные черты в глиняной фигуре. Местная игрушка хранит собственный образ героя, узнаваемый по силуэту.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему плоский рисунок иначе смотрится на объёме?</t>
+          <t xml:space="preserve">Цветок Полховского Майдана ложится на округлую поверхность. Роспись рассчитана на объём: рисунок продолжается за пределами одного взгляда.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сделать так, чтобы каждая фигура вошла в следующую?</t>
+          <t xml:space="preserve">Матрёшки должны войти одна в другую. Размер каждой фигурки связан с соседними — точность токарной работы удерживает расписную семью вместе.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что гремит в игрушке, у которой ничего не видно?</t>
+          <t xml:space="preserve">Внутри берестяного шаркунка спрятан источник звука. Переплетённая оболочка превращает движение руки в слышимый ответ маленькой игрушки.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли найти ручную работу по двум похожим предметам?</t>
+          <t xml:space="preserve">Ручные вещи немного различаются даже в одном ряду. След инструмента и ладони сохраняет решения мастера, которые не повторяются совершенно одинаково.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему изогнутое лезвие удобно для выбранного движения?</t>
+          <t xml:space="preserve">Серп работает с горстью стеблей, удержанной рукой. Жатва складывается из множества повторённых движений — урожай собирают в человеческом масштабе.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как календарный день связывали с переменами погоды?</t>
+          <t xml:space="preserve">Ильин день входит в народный рассказ о перемене лета. Календарная память соединяет праздник с сезонными наблюдениями, не превращая их в прогноз.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как охапка стеблей превращается в удобный груз?</t>
+          <t xml:space="preserve">Сноп придаёт срезанным стеблям переносную форму. Урожай становится отдельной связкой, которую можно поднять, поставить и перевезти.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли связать стебли без покупной верёвки?</t>
+          <t xml:space="preserve">Перевясло делают из самого растительного материала. Часть урожая удерживает другую часть — простое крепление рождается прямо во время работы.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем наряд для работы отличается от праздничного?</t>
+          <t xml:space="preserve">Жнивная рубаха принадлежит тяжёлой поре полевых работ. Крой и материал помогают увидеть связь одежды с движением и сезонной нагрузкой.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто присматривает за младшими, пока взрослые жнут?</t>
+          <t xml:space="preserve">В семейной работе на поле было несколько ролей. Детское участие требует увидеть конкретное занятие, а не переносить взрослый труд на всех одинаково.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему завершение жатвы не всегда означает пустое поле?</t>
+          <t xml:space="preserve">Последние колосья могли оставлять для обрядового действия. Завершение жатвы получало местный смысл, который не сводится к уборке остатка урожая.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему орудие состоит из двух подвижных частей?</t>
+          <t xml:space="preserve">Цеп отделяет зерно ударами по снопам. Подвижное соединение деревянных частей превращает замах человека в работу другого конца орудия.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем снопы везут в особое место?</t>
+          <t xml:space="preserve">Ток — отдельная площадка для работы с урожаем. Расположение снопов и действий показывает, что обмолоту нужен организованный простор.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что делает отдельная постройка, чего не сделает жилая изба?</t>
+          <t xml:space="preserve">В овине снопы готовят к обмолоту. Урожай проходит дополнительный этап обработки, прежде чем зерно отделят от стеблей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как движение воздуха отделяет лёгкое от тяжёлого?</t>
+          <t xml:space="preserve">Воздух помогает отделить зерно от лёгких примесей. Веялка использует различие материала — невидимый поток становится рабочей силой.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему зерно нельзя просто высыпать где угодно?</t>
+          <t xml:space="preserve">В сусеке зерну отводят отдельное место. Домашний запас требует границ и порядка, чтобы результат одного сезона служил семье дальше.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что рассказывает увеличенная ячейка о собранном продукте?</t>
+          <t xml:space="preserve">Медовый сот приносит природную структуру в хозяйство человека. Пасечный труд начинается с внимания к тому, что создают сами пчёлы.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как хозяйственный запас входит в календарный обычай?</t>
+          <t xml:space="preserve">На Медовый Спас продукт пасеки становится праздничным даром. Работа с пчёлами входит в годовой круг встреч, угощения и благодарности.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что остаётся ценным после извлечения мёда?</t>
+          <t xml:space="preserve">Пасека даёт не только мёд, но и воск. Один хозяйственный мир снабжает человека разными материалами, каждому из которых находится своё применение.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плод становится зимним запасом?</t>
+          <t xml:space="preserve">Мочёные яблоки меняют вкус во время хранения. Заготовка превращает летний плод в другой опыт домашней еды, доступный после сбора урожая.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему после сушки меняются размер и способ хранения?</t>
+          <t xml:space="preserve">При сушке грибы становятся легче и занимают меньше места. Лесной сбор получает форму запаса — результат сохраняют отдельной домашней работой.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему для ягод важны форма и глубина корзины?</t>
+          <t xml:space="preserve">Ягодное лукошко должно донести хрупкий сбор. Плетёная форма рассчитана на содержимое: труд собирателя продолжается дорогой домой.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает яблоко, семейный стол и церковный календарь?</t>
+          <t xml:space="preserve">Яблочный Спас связывает плоды с праздничной историей. Сезонный урожай появляется в угощении и обычае конкретного местного сообщества.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Всегда ли кисель был сладким напитком?</t>
+          <t xml:space="preserve">Знакомое слово «кисель» хранит историю другого блюда. Сравнение старого и нового стола показывает, как название переживает перемены приготовления.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем готовая мука отличается от просто размолотого зерна?</t>
+          <t xml:space="preserve">Толокно — результат нескольких этапов подготовки зерна. За простой домашней пищей скрыто время работы, которого не видно в готовой порции.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем рассматривать посуду сбоку, а не только спереди?</t>
+          <t xml:space="preserve">Просвет в кваснике делает сосуд узнаваемым. Необычная форма предлагает рассмотреть устройство бытовой вещи со всех сторон, а не только спереди.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как напиток переносили и разливали покупателям?</t>
+          <t xml:space="preserve">Сбитенник связан с горячим напитком и уличным угощением. Специальный сосуд выводит домашнее тепло в пространство городской встречи.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у одной семьи бывают разные правила трапезы?</t>
+          <t xml:space="preserve">Постный и скоромный стол различаются набором продуктов. Годовой календарь меняет повседневный выбор еды, не меняя саму потребность накормить семью.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как положить заготовку туда, куда рукой не достать?</t>
+          <t xml:space="preserve">Длинная хлебная лопата достигает глубины печи. Расстояние между руками и жаром превращено в размер простого деревянного инструмента.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему богатый запас всё равно делят?</t>
+          <t xml:space="preserve">Часть зерна оставляют для нового посева. Урожай одновременно кормит сегодня и сохраняет возможность следующего года — весь запас съесть нельзя.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему путь к ткани проходит через воду?</t>
+          <t xml:space="preserve">Лён меняется на мочиле ещё до прядения. Будущая нить начинается с обработки стебля, когда ткань пока невозможно увидеть в материале.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздник соседствует с заботой об урожае?</t>
+          <t xml:space="preserve">Успение входит в народную память о завершении лета. Праздник встречается с хозяйственным сезоном, но местный порядок работ требует отдельного рассказа.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему один день называется разными дарами?</t>
+          <t xml:space="preserve">Ореховый, Хлебный и Холщовый — имена одного Спаса. Разные названия сохраняют несколько хозяйственных связей внутри общей праздничной даты.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куда уходит стебель после обмолота?</t>
+          <t xml:space="preserve">Солома служит подстилкой после того, как зерно убрано. У урожая оказывается больше одной полезной части — хозяйство продолжает использовать растение.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочему животному посвящали особый день?</t>
+          <t xml:space="preserve">День Флора и Лавра связан с заботой о лошадях. Праздничное внимание обращено к животному, чья сила участвовала в ежедневном человеческом труде.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что ребёнок несёт из дома в школу?</t>
+          <t xml:space="preserve">Первый ранец собирает школьные вещи в дорожный набор. Учёба становится ежедневным выходом из дома — новый порядок жизни виден в одном предмете.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему старая тетрадь хранит след нажима?</t>
+          <t xml:space="preserve">Перьевая ручка оставляет строку по движению руки. Нажим и направление становятся частью письма: инструмент требует освоенного телесного навыка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как повтор помогает обрести навык?</t>
+          <t xml:space="preserve">Одинаковые буквы в прописи готовят собственный почерк. Повторение даёт руке уверенность, прежде чем запись начнёт отличаться личным движением.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сохранить написанное, не размазав его?</t>
+          <t xml:space="preserve">Промокательная бумага помогает ещё мокрой строке. Маленькая школьная принадлежность хранит способ письма, которому требовалось время на высыхание.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как посчитать покупку без записи столбиком?</t>
+          <t xml:space="preserve">На счётах число видно по положению косточек. Движение пальцев меняет запись и расчёт — абстрактное количество получает материальную форму.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему покупателю важно смотреть на гирю?</t>
+          <t xml:space="preserve">Клеймо на гире связано с доверием к мере. Маленький груз участвует в сделке, где покупателю и продавцу важно одинаково понимать вес.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одно противовесное устройство заменяет две чаши?</t>
+          <t xml:space="preserve">Безмен взвешивает груз на подвеске. Компактное устройство переводит тяжесть вещи в положение, по которому человек узнаёт меру.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему мерка должна быть понятна обеим сторонам?</t>
+          <t xml:space="preserve">Аршином отмеряют ткань для продажи. Будущий наряд начинается с длины полотна — привычная мера связывает торговлю с работой портного.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как найти нужное среди множества торговцев?</t>
+          <t xml:space="preserve">Ярмарочные покупки складываются в путь между рядами. Торговое пространство организует встречу разных нужд, товаров и человеческих занятий.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие слова убеждали покупателя сто лет назад?</t>
+          <t xml:space="preserve">Товарная этикетка обещает качество до открытия упаковки. Надпись и рисунок показывают, как производитель обращается к незнакомому покупателю.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему красивую упаковку не спешат выбрасывать?</t>
+          <t xml:space="preserve">Жестяная коробка остаётся после покупки. Упаковка получает вторую домашнюю жизнь — её содержимое меняется, а след прежнего товара сохраняется.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как вещь помогает откладывать понемногу?</t>
+          <t xml:space="preserve">Копилка собирает небольшие суммы в общий запас. Отдельная монета становится частью будущего решения, которое ещё нельзя оплатить сегодня.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно узнать о семье по списку покупок?</t>
+          <t xml:space="preserve">Домашние расходы попадают в тетрадь. Запись делает хозяйство обозримым: деньги связываются с датами, покупками и памятью о сделанном выборе.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему начало осени могло напоминать новый год?</t>
+          <t xml:space="preserve">Семёнов день отмечают особым местным порядком. Встреча осени получает человеческую форму через действия, которые повторяются в годовом круге.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется распорядок, когда темнеет раньше?</t>
+          <t xml:space="preserve">Новая лучина даёт свет для вечерней работы. С наступлением длинных вечеров домашнее ремесло зависит от маленького, постоянно сменяемого огня.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему продукты отправляют вниз?</t>
+          <t xml:space="preserve">Погреб использует прохладу как часть домашнего устройства. Место хранения помогает урожаю пережить сезон, когда свежий сбор уже закончился.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем большой семье большая ёмкость?</t>
+          <t xml:space="preserve">Капустный запас укладывают в кадку слоями. Большая ёмкость собирает множество малых действий — за зимней порцией стоит общая работа заготовки.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему кухонный инструмент похож на маленький полумесяц?</t>
+          <t xml:space="preserve">Сечка рубит капусту особым лезвием. Назначение инструмента видно в его движении: знакомый продукт требует собственной организации работы.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему хлебный день начинается задолго до печи?</t>
+          <t xml:space="preserve">В квашне тесто оставляют подниматься. Хлеб требует не только движения рук, но и ожидания — домашний труд умеет вовремя остановиться.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сезонная еда остаётся на столе позже?</t>
+          <t xml:space="preserve">Солёные огурцы переносят летний огород в холодный сезон. Заготовка меняет вкус продукта и продлевает путь урожая до семейного стола.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает украшение и знакомый хозяйственный образ?</t>
+          <t xml:space="preserve">Коромысельные серьги напоминают знакомое орудие формой. Бытовое сравнение помогает прочитать устройство украшения, которое носили совсем иначе.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая вещь становится личной?</t>
+          <t xml:space="preserve">Лента и накосник входят в причёску как подарок. Личная вещь соединяет украшение волос с памятью о человеке, который её преподнёс.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее — вместительность или содержимое?</t>
+          <t xml:space="preserve">Сундук невесты собирает вещи, подготовленные к новой жизни. За наполнением стоит запас семейного труда, который нельзя измерить одним размером сундука.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как семья показывала подготовку к свадьбе?</t>
+          <t xml:space="preserve">Приданое выставляют на обозрение. Ткань, швы и отделка делают мастерство видимым другим людям — домашний труд получает общественную оценку.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как временный заработок меняет домашний календарь?</t>
+          <t xml:space="preserve">Осенний наём выводит работника за пределы деревни. Дорога связывает семейное хозяйство с чужой работой и новым порядком повседневной жизни.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие детали портрета были специально подготовлены?</t>
+          <t xml:space="preserve">В фотоателье человек выбирает, как предстать перед камерой. Костюм, поза и обстановка превращают снимок в подготовленное личное представление.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему календарное название приводит на кухню?</t>
+          <t xml:space="preserve">В народном описании Воздвижения появляются капустные хлопоты. Праздничное имя встречается с сезонной заготовкой семейного стола.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что исчезает, когда фотография остаётся без пояснения?</t>
+          <t xml:space="preserve">Подпись в альбоме сохраняет имя рядом с лицом. Несколько слов могут удержать связь поколений, которую само изображение уже не объясняет.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли восстановить дорогу письма по отметкам?</t>
+          <t xml:space="preserve">Почтовый адрес превращает конверт в маршрут. Имя получателя и название места помогают личному письму пройти через незнакомые руки.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что заплата рассказывает о заботе?</t>
+          <t xml:space="preserve">Осенняя починка даёт одежде ещё один сезон. След ремонта показывает заботу о вещи и умение продолжить её службу вместо немедленной замены.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
